--- a/examples/HFP_robin.xlsx
+++ b/examples/HFP_robin.xlsx
@@ -494,7 +494,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6500</v>
+        <v>13500</v>
       </c>
       <c r="I2" t="n">
         <v>7000</v>
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6500</v>
+        <v>14000</v>
       </c>
       <c r="I3" t="n">
         <v>7000</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7500</v>
+        <v>14500</v>
       </c>
       <c r="I4" t="n">
         <v>7500</v>
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="n">
         <v>7500</v>
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>7500</v>
+        <v>15500</v>
       </c>
       <c r="I6" t="n">
         <v>7500</v>

--- a/examples/HFP_robin.xlsx
+++ b/examples/HFP_robin.xlsx
@@ -1123,7 +1123,7 @@
         <v>300000</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>

--- a/examples/HFP_robin.xlsx
+++ b/examples/HFP_robin.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robin" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Robin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Debts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fixed Assets" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,15 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -493,13 +498,21 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>13500</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>7000</v>
       </c>
-      <c r="L2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -516,13 +529,21 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>14000</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>7000</v>
       </c>
-      <c r="L3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>3650</v>
       </c>
     </row>
@@ -539,13 +560,21 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>14500</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>7500</v>
       </c>
-      <c r="L4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>3850</v>
       </c>
     </row>
@@ -562,13 +591,21 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>15000</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>7500</v>
       </c>
-      <c r="L5" t="n">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>4150</v>
       </c>
     </row>
@@ -585,13 +622,21 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>15500</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="L6" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>4300</v>
       </c>
     </row>
@@ -599,13 +644,24 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -613,13 +669,24 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -627,13 +694,24 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -641,13 +719,24 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -655,13 +744,24 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -669,13 +769,24 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,13 +794,24 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -697,13 +819,24 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -711,13 +844,24 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -725,13 +869,24 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -739,13 +894,24 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -753,13 +919,24 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -767,13 +944,24 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -781,13 +969,24 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -795,13 +994,24 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -809,13 +1019,24 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -823,13 +1044,24 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -837,13 +1069,24 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -851,13 +1094,24 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,13 +1119,24 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -879,13 +1144,24 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -893,13 +1169,24 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -907,13 +1194,24 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -921,13 +1219,24 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -935,13 +1244,24 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -949,13 +1269,24 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -963,13 +1294,24 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -977,13 +1319,24 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>

--- a/examples/HFP_robin.xlsx
+++ b/examples/HFP_robin.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,15 +471,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -498,21 +503,16 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>13500</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>7000</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -529,21 +529,16 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>14000</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>7000</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>3650</v>
       </c>
     </row>
@@ -560,21 +555,16 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>14500</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>7500</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>3850</v>
       </c>
     </row>
@@ -591,21 +581,16 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>15000</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>7500</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>4150</v>
       </c>
     </row>
@@ -622,21 +607,16 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>15500</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>4300</v>
       </c>
     </row>
@@ -644,24 +624,16 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -669,24 +641,16 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -694,24 +658,16 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -719,24 +675,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -744,24 +692,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -769,24 +709,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -794,24 +726,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,24 +743,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,24 +760,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,24 +777,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -894,24 +794,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -919,24 +811,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -944,24 +828,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -969,24 +845,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -994,24 +862,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1019,24 +879,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1044,24 +896,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1069,24 +913,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1094,24 +930,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1119,24 +947,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1144,24 +964,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1169,24 +981,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1194,24 +998,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1219,24 +1015,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1244,24 +1032,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1269,24 +1049,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1294,24 +1066,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1319,24 +1083,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
